--- a/artfynd/A 15237-2022 artfynd.xlsx
+++ b/artfynd/A 15237-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15237-2022 artfynd.xlsx
+++ b/artfynd/A 15237-2022 artfynd.xlsx
@@ -14827,7 +14827,7 @@
         <v>114052520</v>
       </c>
       <c r="B128" t="n">
-        <v>86438</v>
+        <v>86445</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>

--- a/artfynd/A 15237-2022 artfynd.xlsx
+++ b/artfynd/A 15237-2022 artfynd.xlsx
@@ -4610,11 +4610,11 @@
         <v>111492510</v>
       </c>
       <c r="B37" t="n">
-        <v>89845</v>
+        <v>91168</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519614.8458918218</v>
+        <v>519615</v>
       </c>
       <c r="R37" t="n">
-        <v>7115936.507650574</v>
+        <v>7115936</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4680,19 +4680,9 @@
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 15237-2022 artfynd.xlsx
+++ b/artfynd/A 15237-2022 artfynd.xlsx
@@ -4610,7 +4610,7 @@
         <v>111492510</v>
       </c>
       <c r="B37" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 15237-2022 artfynd.xlsx
+++ b/artfynd/A 15237-2022 artfynd.xlsx
@@ -4610,7 +4610,7 @@
         <v>111492510</v>
       </c>
       <c r="B37" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 15237-2022 artfynd.xlsx
+++ b/artfynd/A 15237-2022 artfynd.xlsx
@@ -4610,7 +4610,7 @@
         <v>111492510</v>
       </c>
       <c r="B37" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 15237-2022 artfynd.xlsx
+++ b/artfynd/A 15237-2022 artfynd.xlsx
@@ -4610,7 +4610,7 @@
         <v>111492510</v>
       </c>
       <c r="B37" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 15237-2022 artfynd.xlsx
+++ b/artfynd/A 15237-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY153"/>
+  <dimension ref="A1:AZ153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492483</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492523</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480257</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492463</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111929288</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492503</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492488</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476231</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480081</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480082</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492449</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492450</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492452</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480411</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480412</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480413</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480414</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492490</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492526</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477225</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111478348</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480232</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492459</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492460</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492461</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492510</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476235</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476236</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3586,6 +3736,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477227</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3683,6 +3838,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477229</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3780,6 +3940,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477420</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3877,6 +4042,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111478349</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3974,6 +4144,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111478350</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4071,6 +4246,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111478351</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4168,6 +4348,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480266</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4265,6 +4450,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480272</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4362,6 +4552,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480273</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4459,6 +4654,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480274</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4556,6 +4756,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480275</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4653,6 +4858,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480276</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4750,6 +4960,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480277</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4847,6 +5062,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480278</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4944,6 +5164,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480279</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5041,6 +5266,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492465</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5138,6 +5368,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492466</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5235,6 +5470,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492467</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5332,6 +5572,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492468</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5429,6 +5674,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492469</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5526,6 +5776,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492470</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5623,6 +5878,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492471</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5720,6 +5980,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492512</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5817,6 +6082,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492513</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5915,6 +6185,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492514</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6031,6 +6306,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480226</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6132,6 +6412,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477231</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6229,6 +6514,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477421</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6326,6 +6616,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477432</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6423,6 +6718,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477433</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6520,6 +6820,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480283</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6617,6 +6922,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480284</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6714,6 +7024,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492473</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6811,6 +7126,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492516</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6908,6 +7228,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111929291</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7005,6 +7330,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492487</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7102,6 +7432,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477418</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7199,6 +7534,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480201</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7296,6 +7636,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480203</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7393,6 +7738,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492458</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7490,6 +7840,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492508</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7587,6 +7942,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492481</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7684,6 +8044,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476232</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7781,6 +8146,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480100</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7878,6 +8248,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111481875</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7975,6 +8350,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492453</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8072,6 +8452,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492454</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8169,6 +8554,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492504</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8266,6 +8656,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492505</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8374,6 +8769,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114052520</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8471,6 +8871,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480436</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8568,6 +8973,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492491</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8665,6 +9075,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492448</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8762,6 +9177,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477233</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8859,6 +9279,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477235</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8956,6 +9381,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480456</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9053,6 +9483,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480457</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9150,6 +9585,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480459</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9247,6 +9687,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480460</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9344,6 +9789,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492492</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9441,6 +9891,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492493</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9538,6 +9993,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492494</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9635,6 +10095,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492495</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9732,6 +10197,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492496</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9829,6 +10299,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492497</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9926,6 +10401,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492498</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10023,6 +10503,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492499</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10120,6 +10605,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492500</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10217,6 +10707,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111481876</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10314,6 +10809,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492462</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10415,6 +10915,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477223</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10512,6 +11017,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477417</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10609,6 +11119,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477430</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10706,6 +11221,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477431</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10803,6 +11323,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480055</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10900,6 +11425,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480056</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10997,6 +11527,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492446</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11094,6 +11629,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476237</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11191,6 +11731,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477422</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11288,6 +11833,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480325</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11385,6 +11935,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480326</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11482,6 +12037,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480327</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11579,6 +12139,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492474</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11676,6 +12241,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492475</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11773,6 +12343,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492518</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11870,6 +12445,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492519</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11967,6 +12547,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477242</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12064,6 +12649,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480533</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12161,6 +12751,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480534</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12258,6 +12853,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480535</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12355,6 +12955,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480543</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12452,6 +13057,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492531</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12563,6 +13173,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111528017</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12660,6 +13275,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480150</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12757,6 +13377,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492456</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12854,6 +13479,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492457</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12951,6 +13581,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480342</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13048,6 +13683,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480343</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13145,6 +13785,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480344</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13242,6 +13887,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492479</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13339,6 +13989,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492480</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13455,6 +14110,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492520</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13555,6 +14215,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111811085</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13652,6 +14317,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480163</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13749,6 +14419,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480225</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13846,6 +14521,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480134</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13943,6 +14623,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480017</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14040,6 +14725,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480388</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14137,6 +14827,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480394</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14234,6 +14929,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480370</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14331,6 +15031,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480371</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14428,6 +15133,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492486</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14525,6 +15235,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492522</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14622,6 +15337,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480007</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14719,6 +15439,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480011</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14816,6 +15541,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111481874</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14913,6 +15643,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111481872</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15019,6 +15754,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111528096</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15116,6 +15856,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480137</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15213,6 +15958,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480138</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15310,6 +16060,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492455</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15407,6 +16162,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492507</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15504,8 +16264,167 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111492489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>